--- a/fixtures/acfc_shapes/pair_4/sttm_nb_cob_report.xlsx
+++ b/fixtures/acfc_shapes/pair_4/sttm_nb_cob_report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,130 +516,124 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stage Layer</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Standard Layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Length</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Segment</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Catalog</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>TableName</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>ColumnName</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>DataType</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Primary Key</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Record Type</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>stg_nb_cob</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>nb_cob_report_hdr</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>RECORD_TYPE</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Schema</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>TableName</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>ColumnName</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>DataType</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Primary Key</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>File Name</t>
+          <t>Record Type</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -648,7 +642,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -657,7 +651,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -672,7 +666,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FILE_NAME</t>
+          <t>RECORD_TYPE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -693,11 +687,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>File Creation Date</t>
+          <t>File Name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -706,7 +700,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -715,7 +709,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -730,7 +724,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FILE_CREATION_DATE</t>
+          <t>FILE_NAME</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -744,6 +738,41 @@
         </is>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>FILE_NAME</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -751,11 +780,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>File Creation Time</t>
+          <t>File Creation Date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -764,7 +793,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -773,7 +802,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -788,7 +817,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>FILE_CREATION_TIME</t>
+          <t>FILE_CREATION_DATE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -798,10 +827,45 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>FILE_CREATION_DATE</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -809,11 +873,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vendor Name</t>
+          <t>File Creation Time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -822,7 +886,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -831,7 +895,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -846,7 +910,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>VENDOR_NAME</t>
+          <t>FILE_CREATION_TIME</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -856,10 +920,45 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>FILE_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -867,11 +966,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LOB</t>
+          <t>Vendor Name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -880,7 +979,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -889,7 +988,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -904,7 +1003,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LOB</t>
+          <t>VENDOR_NAME</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -918,6 +1017,41 @@
         </is>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>VENDOR_NAME</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -925,11 +1059,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Report Period Start</t>
+          <t>LOB</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -938,7 +1072,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -947,7 +1081,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -962,7 +1096,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>REPORT_PERIOD_START</t>
+          <t>LOB</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -976,6 +1110,41 @@
         </is>
       </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>LOB</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -983,11 +1152,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Report Period End</t>
+          <t>Report Period Start</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1005,7 +1174,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1020,72 +1189,148 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>REPORT_PERIOD_START</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>REPORT_PERIOD_START_DATE</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Report Period End</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PR_DLK</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>stg_nb_cob</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>REPORT_PERIOD_END</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>stg_nb_cob</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>nb_cob_report_hdr</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>SRC_FILE_NAME</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>REPORT_PERIOD_END_DATE</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1109,7 +1354,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1124,12 +1369,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>REC_CREATION_TIME</t>
+          <t>SRC_FILE_NAME</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Timestamp</t>
+          <t>String</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1138,6 +1383,41 @@
         </is>
       </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SRC_FILE_NAME</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1161,7 +1441,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1176,78 +1456,142 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>REC_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>REC_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PR_DLK</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>stg_nb_cob</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>REC_UPDATED_TIME</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Record Type</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>stg_nb_cob</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>nb_cob_report_dtl</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>RECORD_TYPE</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>nb_cob_report_hdr</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>REC_UPDATED_TIME</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1255,11 +1599,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LOB</t>
+          <t>Record Type</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1268,7 +1612,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1277,7 +1621,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1292,7 +1636,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LOB</t>
+          <t>RECORD_TYPE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1313,11 +1657,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Member ID</t>
+          <t>LOB</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1326,7 +1670,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1335,7 +1679,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1350,7 +1694,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MEMBER_ID</t>
+          <t>LOB</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1365,17 +1709,52 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>LOB</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Subscriber ID</t>
+          <t>Member ID</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1393,7 +1772,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1408,7 +1787,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SUBSCRIBER_ID</t>
+          <t>MEMBER_ID</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1423,17 +1802,52 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Member Last Name</t>
+          <t>Subscriber ID</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1442,7 +1856,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1451,7 +1865,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1466,7 +1880,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MEMBER_LAST_NAME</t>
+          <t>SUBSCRIBER_ID</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1476,10 +1890,45 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUBSCRIBER_ID</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1487,11 +1936,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Member First Name</t>
+          <t>Member Last Name</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1500,7 +1949,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1509,7 +1958,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1524,7 +1973,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MEMBER_FIRST_NAME</t>
+          <t>MEMBER_LAST_NAME</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1538,6 +1987,41 @@
         </is>
       </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>MEMBER_LAST_NAME</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1545,11 +2029,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Member Date of Birth</t>
+          <t>Member First Name</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1558,7 +2042,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1567,7 +2051,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1582,7 +2066,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MEMBER_DOB</t>
+          <t>MEMBER_FIRST_NAME</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1592,10 +2076,45 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>MEMBER_FIRST_NAME</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1603,11 +2122,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Member Gender</t>
+          <t>Member Date of Birth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1616,7 +2135,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1625,7 +2144,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1640,7 +2159,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MEMBER_GENDER</t>
+          <t>MEMBER_DOB</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1650,10 +2169,45 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>MEMBER_BIRTH_DATE</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1661,11 +2215,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Other Carrier ID</t>
+          <t>Member Gender</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1674,7 +2228,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1683,7 +2237,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1698,7 +2252,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OTHER_CARRIER_ID</t>
+          <t>MEMBER_GENDER</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1708,22 +2262,57 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>MEMBER_GENDER</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other Carrier Name</t>
+          <t>Other Carrier ID</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1732,7 +2321,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1741,7 +2330,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1756,7 +2345,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OTHER_CARRIER_NAME</t>
+          <t>OTHER_CARRIER_ID</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1766,22 +2355,57 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>OTHER_CARRIER_ID</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Other Policy Number</t>
+          <t>Other Carrier Name</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1790,7 +2414,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1799,7 +2423,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1814,7 +2438,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>OTHER_POLICY_NUMBER</t>
+          <t>OTHER_CARRIER_NAME</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1824,10 +2448,45 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>OTHER_CARRIER_NAME</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1835,11 +2494,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Other Group Number</t>
+          <t>Other Policy Number</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1857,7 +2516,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1872,7 +2531,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>OTHER_GROUP_NUMBER</t>
+          <t>OTHER_POLICY_NUMBER</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1882,10 +2541,45 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>OTHER_POLICY_NUMBER</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1893,11 +2587,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coverage Type</t>
+          <t>Other Group Number</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1906,7 +2600,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1915,7 +2609,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1930,7 +2624,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COVERAGE_TYPE</t>
+          <t>OTHER_GROUP_NUMBER</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1940,10 +2634,45 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>OTHER_GROUP_NUMBER</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -1951,11 +2680,11 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COB Order</t>
+          <t>Coverage Type</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1964,7 +2693,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1973,7 +2702,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1988,7 +2717,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COB_ORDER</t>
+          <t>COVERAGE_TYPE</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2002,6 +2731,41 @@
         </is>
       </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>COVERAGE_TYPE</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2009,11 +2773,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>COB Effective Date</t>
+          <t>COB Order</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2022,7 +2786,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2031,7 +2795,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2046,7 +2810,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COB_EFF_DATE</t>
+          <t>COB_ORDER</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2061,17 +2825,52 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>COB_ORDER</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>COB Termination Date</t>
+          <t>COB Effective Date</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2089,7 +2888,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2104,7 +2903,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COB_TERM_DATE</t>
+          <t>COB_EFF_DATE</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2114,22 +2913,57 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>COB_EFF_DATE</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Medicare Indicator</t>
+          <t>COB Termination Date</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2138,7 +2972,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2147,7 +2981,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2162,7 +2996,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MEDICARE_IND</t>
+          <t>COB_TERM_DATE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2176,6 +3010,41 @@
         </is>
       </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>COB_TERM_DATE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2183,11 +3052,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Source of Information</t>
+          <t>Medicare Indicator</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2196,7 +3065,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2205,7 +3074,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2220,7 +3089,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SOURCE_OF_INFO</t>
+          <t>MEDICARE_IND</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2234,6 +3103,41 @@
         </is>
       </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>MEDICARE_IND</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2241,11 +3145,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Verification Date</t>
+          <t>Source of Information</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2254,7 +3158,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2263,7 +3167,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2278,7 +3182,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>VERIFICATION_DATE</t>
+          <t>SOURCE_OF_INFO</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2292,6 +3196,41 @@
         </is>
       </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SOURCE_OF_INFO</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2299,109 +3238,185 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>27</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Verification Date</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>8</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PR_DLK</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>stg_nb_cob</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>VERIFICATION_DATE</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>VERIFICATION_DATE</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>28</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PR_DLK</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>stg_nb_cob</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>nb_cob_report_dtl</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>RECORD_STATUS</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>stg_nb_cob</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>nb_cob_report_dtl</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>SRC_FILE_NAME</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>RECORD_STATUS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2425,7 +3440,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2440,12 +3455,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>REC_CREATION_TIME</t>
+          <t>SRC_FILE_NAME</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Timestamp</t>
+          <t>String</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2454,6 +3469,41 @@
         </is>
       </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SRC_FILE_NAME</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2477,7 +3527,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2492,78 +3542,142 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>REC_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>REC_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PR_DLK</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>stg_nb_cob</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>REC_UPDATED_TIME</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>29</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Record Type</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Trailer</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>stg_nb_cob</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>nb_cob_report_trl</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>RECORD_TYPE</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>nb_cob_report_dtl</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>REC_UPDATED_TIME</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2571,11 +3685,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>File Name</t>
+          <t>Record Type</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2584,7 +3698,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2593,7 +3707,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2608,7 +3722,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>FILE_NAME</t>
+          <t>RECORD_TYPE</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2629,11 +3743,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Detail Record Count</t>
+          <t>File Name</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2642,7 +3756,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2651,7 +3765,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2666,7 +3780,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DETAIL_RECORD_COUNT</t>
+          <t>FILE_NAME</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2680,6 +3794,41 @@
         </is>
       </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>nb_cob_report_trl</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>FILE_NAME</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2687,11 +3836,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Total Record Count</t>
+          <t>Detail Record Count</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2709,7 +3858,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2724,7 +3873,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TOTAL_RECORD_COUNT</t>
+          <t>DETAIL_RECORD_COUNT</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2738,6 +3887,41 @@
         </is>
       </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>nb_cob_report_trl</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DETAIL_RECORD_COUNT</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2745,11 +3929,11 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>File Creation Date</t>
+          <t>Total Record Count</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2758,7 +3942,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2767,7 +3951,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2782,7 +3966,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>FILE_CREATION_DATE</t>
+          <t>TOTAL_RECORD_COUNT</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2796,6 +3980,41 @@
         </is>
       </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>nb_cob_report_trl</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>TOTAL_RECORD_COUNT</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2803,109 +4022,185 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
+        <v>33</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>File Creation Date</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Trailer</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PR_DLK</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>stg_nb_cob</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>nb_cob_report_trl</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>FILE_CREATION_DATE</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>nb_cob_report_trl</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>FILE_CREATION_DATE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
         <v>34</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>End of File Marker</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>3</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Trailer</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PR_DLK</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>stg_nb_cob</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>nb_cob_report_trl</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>END_OF_FILE_MARKER</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Trailer</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>stg_nb_cob</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>nb_cob_report_trl</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>SRC_FILE_NAME</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>END_OF_FILE_MARKER</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2929,7 +4224,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2944,12 +4239,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>REC_CREATION_TIME</t>
+          <t>SRC_FILE_NAME</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Timestamp</t>
+          <t>String</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -2958,6 +4253,41 @@
         </is>
       </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>nb_cob_report_trl</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SRC_FILE_NAME</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -2981,7 +4311,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>PR_DLK</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2996,26 +4326,153 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t>REC_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>nb_cob_report_trl</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>REC_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Trailer</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PR_DLK</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>stg_nb_cob</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>nb_cob_report_trl</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>REC_UPDATED_TIME</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>PR_STD</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>nb_cob</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>nb_cob_report_trl</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>REC_UPDATED_TIME</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="F10:L10"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="M10:S10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3133,7 +4590,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3175,7 +4632,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3217,7 +4674,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3259,7 +4716,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3301,7 +4758,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3343,7 +4800,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3385,7 +4842,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3427,7 +4884,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3469,7 +4926,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3511,7 +4968,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3575,7 +5032,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3617,7 +5074,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3659,7 +5116,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3701,7 +5158,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3743,7 +5200,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3785,7 +5242,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3827,7 +5284,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3869,7 +5326,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3911,7 +5368,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3953,7 +5410,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3995,7 +5452,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4037,7 +5494,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4079,7 +5536,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4121,7 +5578,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4163,7 +5620,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4205,7 +5662,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4247,7 +5704,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4289,7 +5746,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4331,7 +5788,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4373,7 +5830,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4415,7 +5872,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4457,7 +5914,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4521,7 +5978,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4563,7 +6020,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4605,7 +6062,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4647,7 +6104,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4689,7 +6146,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4731,7 +6188,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4773,7 +6230,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4815,7 +6272,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>cob</t>
+          <t>nb_cob</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
